--- a/data/trending_integrated_20260921_15.xlsx
+++ b/data/trending_integrated_20260921_15.xlsx
@@ -584,7 +584,7 @@
         <v>134</v>
       </c>
       <c r="G2" t="n">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>204334494035</v>
+        <v>204398906785</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>美 타임지 선정 '세계 최고 헬스테크 기업' 그룹 선정. 2주간의 폭락 후 반등 조짐.</t>
+          <t>美 타임지 선정 '세계 최고 헬스테크 기업' 선정 소식에 따른 주가 급등. 향후 추가 상승 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['헬스테크', '타임지 선정', '주가 반등']</t>
+          <t>['헬스테크', '타임지선정', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10640</v>
+        <v>10570</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.96%</t>
+          <t>'+17.18%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.09</v>
       </c>
       <c r="E3" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F3" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G3" t="n">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="H3" t="n">
         <v>8.6</v>
@@ -702,7 +702,7 @@
         <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>268545987085</v>
+        <v>272532022840</v>
       </c>
       <c r="P3" t="n">
         <v>11640</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>강한 거래대금 동반하며 전고점 돌파 기대. 후공정 대장주로서 2만 및 5만 목표.</t>
+          <t>강한 거래대금을 동반한 주가 상승세, 후공정 대장주로서의 기대감. 향후 연간 수익성 개선 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['거래대금', '후공정', '대장주']</t>
+          <t>['거래대금', '후공정', '수익성']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20800</v>
+        <v>20650</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.62%</t>
+          <t>'+11.80%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="F4" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G4" t="n">
-        <v>315</v>
+        <v>351</v>
       </c>
       <c r="H4" t="n">
         <v>1.25</v>
@@ -794,7 +794,7 @@
         <v>0.98</v>
       </c>
       <c r="O4" t="n">
-        <v>127293116845</v>
+        <v>129778796995</v>
       </c>
       <c r="P4" t="n">
         <v>21950</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>혈관 치료 기술 확장 및 글로벌 임상 3상 진입 소식. MSD의 EyeBio 인수 사례 언급.</t>
+          <t>국내 유일 혈관 치료 기술 확장 기대감. 글로벌 3상 동시 돌입 소식에 따른 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['신약 개발', '임상 3상', 'ADC']</t>
+          <t>['혈관치료', '3상돌입', '기술확장']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31950</v>
+        <v>32000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.76%</t>
+          <t>'+7.93%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.48</v>
       </c>
       <c r="E5" t="n">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="F5" t="n">
         <v>290</v>
       </c>
       <c r="G5" t="n">
-        <v>2274</v>
+        <v>2296</v>
       </c>
       <c r="H5" t="n">
         <v>16.67</v>
@@ -886,7 +886,7 @@
         <v>17.15</v>
       </c>
       <c r="O5" t="n">
-        <v>44235160600</v>
+        <v>44773437825</v>
       </c>
       <c r="P5" t="n">
         <v>69200</v>
@@ -946,13 +946,13 @@
         <v>-0.31</v>
       </c>
       <c r="E6" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F6" t="n">
         <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H6" t="n">
         <v>0.19</v>
@@ -978,7 +978,7 @@
         <v>0.5</v>
       </c>
       <c r="O6" t="n">
-        <v>62924071015</v>
+        <v>63216838860</v>
       </c>
       <c r="P6" t="n">
         <v>13140</v>
@@ -1038,13 +1038,13 @@
         <v>-0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F7" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G7" t="n">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="H7" t="n">
         <v>75.44</v>
@@ -1070,7 +1070,7 @@
         <v>75.53</v>
       </c>
       <c r="O7" t="n">
-        <v>765089960800</v>
+        <v>781078743050</v>
       </c>
       <c r="P7" t="n">
         <v>243500</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11020</v>
+        <v>11030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.75%</t>
+          <t>'+4.85%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.16</v>
       </c>
       <c r="E8" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="F8" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G8" t="n">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="H8" t="n">
         <v>18.29</v>
@@ -1162,7 +1162,7 @@
         <v>18.13</v>
       </c>
       <c r="O8" t="n">
-        <v>209365556345</v>
+        <v>210552152555</v>
       </c>
       <c r="P8" t="n">
         <v>22450</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>272750</v>
+        <v>273500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.50%</t>
+          <t>'+4.79%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="G9" t="n">
-        <v>2585</v>
+        <v>2535</v>
       </c>
       <c r="H9" t="n">
         <v>46.46</v>
@@ -1254,7 +1254,7 @@
         <v>46.48</v>
       </c>
       <c r="O9" t="n">
-        <v>5224057081500</v>
+        <v>5347635663750</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>외인 대량 매수에 따른 주가 상승 기대감. 3분기 실적 발표 및 자사주 소각, 배당 관련 언급.</t>
+          <t>외인 매수세 유입에 따른 상승 기대감 존재. 배당금 및 잠정실적 발표 예정.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['배당', '자사주 소각', '실적 발표']</t>
+          <t>['배당금', '실적발표', '외인매수']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1866000</v>
+        <v>1861000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.48%</t>
+          <t>'+0.22%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="G10" t="n">
-        <v>2316</v>
+        <v>2306</v>
       </c>
       <c r="H10" t="n">
         <v>50.23</v>
@@ -1346,7 +1346,7 @@
         <v>50.1</v>
       </c>
       <c r="O10" t="n">
-        <v>4222681976000</v>
+        <v>4346854184500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>신한증권 앱 오류 관련 불만 속에서 주가 반등 기대감. 반도체 수출 지표 및 2시 이후 반등 가능성 언급.</t>
+          <t>반도체 수출 호조 기대감 속 주가 상승 전망. 신한증권 전산 오류로 인한 불편 호소.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체 수출', '신한증권', '반등']</t>
+          <t>['반도체수출', '신한증권', '주가상승']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26600</v>
+        <v>26650</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.75%</t>
+          <t>'-0.56%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.3</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F11" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G11" t="n">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="H11" t="n">
         <v>2.11</v>
@@ -1438,7 +1438,7 @@
         <v>2.41</v>
       </c>
       <c r="O11" t="n">
-        <v>127816938350</v>
+        <v>130399465500</v>
       </c>
       <c r="P11" t="n">
         <v>59600</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>317000</v>
+        <v>318000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.06%</t>
+          <t>'-2.75%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>1.66</v>
       </c>
       <c r="E12" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F12" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G12" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H12" t="n">
         <v>3.62</v>
@@ -1530,7 +1530,7 @@
         <v>1.96</v>
       </c>
       <c r="O12" t="n">
-        <v>95740768750</v>
+        <v>97393623250</v>
       </c>
       <c r="P12" t="n">
         <v>635000</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18290</v>
+        <v>18320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.28%</t>
+          <t>'-3.12%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G13" t="n">
-        <v>510</v>
+        <v>528</v>
       </c>
       <c r="H13" t="n">
         <v>10.74</v>
@@ -1622,7 +1622,7 @@
         <v>10.74</v>
       </c>
       <c r="O13" t="n">
-        <v>83658568300</v>
+        <v>85232207130</v>
       </c>
       <c r="P13" t="n">
         <v>40350</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>공매도 관련 불만 및 대차 해지 운동 촉구. 주가 상승 저지 세력 존재 가능성 언급.</t>
+          <t>공매도 세력에 대한 불만과 주가 상승 의지 표출. 추세 전환 기대감 있으나 근거 부족.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '대차 해지', '주가 조작']</t>
+          <t>['공매도', '대차해지', '주가정상화']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17660</v>
+        <v>13400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.60%</t>
+          <t>'-3.39%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3.29</v>
+        <v>0.58</v>
       </c>
       <c r="E14" t="n">
-        <v>264</v>
+        <v>91</v>
       </c>
       <c r="F14" t="n">
-        <v>157</v>
+        <v>50</v>
       </c>
       <c r="G14" t="n">
-        <v>1188</v>
+        <v>467</v>
       </c>
       <c r="H14" t="n">
-        <v>7.9</v>
+        <v>5.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,91 +1699,91 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18320</v>
+        <v>13870</v>
       </c>
       <c r="K14" t="n">
-        <v>18450</v>
+        <v>14070</v>
       </c>
       <c r="L14" t="n">
-        <v>18590</v>
+        <v>14790</v>
       </c>
       <c r="M14" t="n">
-        <v>17560</v>
+        <v>13350</v>
       </c>
       <c r="N14" t="n">
-        <v>4.61</v>
+        <v>4.92</v>
       </c>
       <c r="O14" t="n">
-        <v>221678244825</v>
+        <v>76443292810</v>
       </c>
       <c r="P14" t="n">
-        <v>31500</v>
+        <v>30200</v>
       </c>
       <c r="Q14" t="n">
-        <v>1272</v>
+        <v>3540</v>
       </c>
       <c r="R14" t="n">
-        <v>-1828000</v>
+        <v>-382000</v>
       </c>
       <c r="S14" t="n">
-        <v>-4000</v>
+        <v>-14000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>기관 매수세와 함께 미국 광통신 AI 주식 급등 수혜 기대. 투자주의 종목 지정 및 CB 발행.</t>
+          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['기관 매수', '광통신 AI', '투자주의']</t>
+          <t>['원전', '신한투자증권', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13370</v>
+        <v>17665</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.60%</t>
+          <t>'-3.58%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.58</v>
+        <v>3.29</v>
       </c>
       <c r="E15" t="n">
-        <v>85</v>
+        <v>266</v>
       </c>
       <c r="F15" t="n">
-        <v>47</v>
+        <v>157</v>
       </c>
       <c r="G15" t="n">
-        <v>464</v>
+        <v>1202</v>
       </c>
       <c r="H15" t="n">
-        <v>5.5</v>
+        <v>7.9</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,244 +1791,244 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>13870</v>
+        <v>18320</v>
       </c>
       <c r="K15" t="n">
-        <v>14070</v>
+        <v>18450</v>
       </c>
       <c r="L15" t="n">
-        <v>14790</v>
+        <v>18590</v>
       </c>
       <c r="M15" t="n">
-        <v>13360</v>
+        <v>17560</v>
       </c>
       <c r="N15" t="n">
-        <v>4.92</v>
+        <v>4.61</v>
       </c>
       <c r="O15" t="n">
-        <v>75602514095</v>
+        <v>225068246005</v>
       </c>
       <c r="P15" t="n">
-        <v>30200</v>
+        <v>31500</v>
       </c>
       <c r="Q15" t="n">
-        <v>3540</v>
+        <v>1272</v>
       </c>
       <c r="R15" t="n">
-        <v>-382000</v>
+        <v>-1828000</v>
       </c>
       <c r="S15" t="n">
-        <v>-14000</v>
+        <v>-4000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
+          <t>기관 매수세와 함께 미국 광통신 AI 주식 급등 수혜 기대. 투자주의 종목 지정 및 CB 발행.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['원전', '신한투자증권', '공매도']</t>
+          <t>['기관 매수', '광통신 AI', '투자주의']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>76900</v>
+        <v>4055</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.88%</t>
+          <t>'-3.91%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.1</v>
+        <v>-0.22</v>
       </c>
       <c r="E16" t="n">
-        <v>180</v>
+        <v>114</v>
       </c>
       <c r="F16" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="G16" t="n">
-        <v>792</v>
+        <v>474</v>
       </c>
       <c r="H16" t="n">
-        <v>10.58</v>
+        <v>0.33</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>80000</v>
+        <v>4220</v>
       </c>
       <c r="K16" t="n">
-        <v>82900</v>
+        <v>4220</v>
       </c>
       <c r="L16" t="n">
-        <v>83000</v>
+        <v>4415</v>
       </c>
       <c r="M16" t="n">
-        <v>75300</v>
+        <v>4005</v>
       </c>
       <c r="N16" t="n">
-        <v>10.68</v>
+        <v>0.55</v>
       </c>
       <c r="O16" t="n">
-        <v>117731776600</v>
+        <v>32991284300</v>
       </c>
       <c r="P16" t="n">
-        <v>184000</v>
+        <v>6480</v>
       </c>
       <c r="Q16" t="n">
-        <v>44750</v>
+        <v>1738</v>
       </c>
       <c r="R16" t="n">
-        <v>-605000</v>
+        <v>264000</v>
       </c>
       <c r="S16" t="n">
-        <v>-17000</v>
+        <v>-4000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>K-방산 '다층 대드론' 새 시장 개척 기대. 공매도 관련 부정적 언급.</t>
+          <t>재료 대비 주가 부진, 물량 넘기기 및 개잡주 평가. 3840 가격대 기다리며 신규 매수 금지 의견.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['K-방산', '드론', '공매도']</t>
+          <t>['주가 부진', '물량 넘기기', '신규 매수 금지']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4030</v>
+        <v>76500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.50%</t>
+          <t>'-4.38%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.22</v>
+        <v>-0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>113</v>
+        <v>184</v>
       </c>
       <c r="F17" t="n">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="G17" t="n">
-        <v>468</v>
+        <v>797</v>
       </c>
       <c r="H17" t="n">
-        <v>0.33</v>
+        <v>10.58</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>4220</v>
+        <v>80000</v>
       </c>
       <c r="K17" t="n">
-        <v>4220</v>
+        <v>82900</v>
       </c>
       <c r="L17" t="n">
-        <v>4415</v>
+        <v>83000</v>
       </c>
       <c r="M17" t="n">
-        <v>4005</v>
+        <v>75300</v>
       </c>
       <c r="N17" t="n">
-        <v>0.55</v>
+        <v>10.68</v>
       </c>
       <c r="O17" t="n">
-        <v>32646819938</v>
+        <v>120251588400</v>
       </c>
       <c r="P17" t="n">
-        <v>6480</v>
+        <v>184000</v>
       </c>
       <c r="Q17" t="n">
-        <v>1738</v>
+        <v>44750</v>
       </c>
       <c r="R17" t="n">
-        <v>264000</v>
+        <v>-605000</v>
       </c>
       <c r="S17" t="n">
-        <v>-4000</v>
+        <v>-17000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>재료 대비 주가 부진, 물량 넘기기 및 개잡주 평가. 3840 가격대 기다리며 신규 매수 금지 의견.</t>
+          <t>K-방산 '다층 대드론' 새 시장 개척 기대. 공매도 관련 부정적 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가 부진', '물량 넘기기', '신규 매수 금지']</t>
+          <t>['K-방산', '드론', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>272210</t>
         </is>
       </c>
     </row>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29925</v>
+        <v>29850</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.85%</t>
+          <t>'-5.09%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2056,7 +2056,7 @@
         <v>70</v>
       </c>
       <c r="G18" t="n">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="H18" t="n">
         <v>11.92</v>
@@ -2076,13 +2076,13 @@
         <v>31550</v>
       </c>
       <c r="M18" t="n">
-        <v>29800</v>
+        <v>29750</v>
       </c>
       <c r="N18" t="n">
         <v>11.44</v>
       </c>
       <c r="O18" t="n">
-        <v>92905196750</v>
+        <v>99435817975</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>27000</v>
+        <v>27100</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-27.81%</t>
+          <t>'-27.54%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G19" t="n">
-        <v>1648</v>
+        <v>1620</v>
       </c>
       <c r="H19" t="n">
         <v>7.09</v>
@@ -2174,7 +2174,7 @@
         <v>7.08</v>
       </c>
       <c r="O19" t="n">
-        <v>120659134075</v>
+        <v>121281027200</v>
       </c>
       <c r="P19" t="n">
         <v>146600</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>급락에 대한 불만 및 주가 조작 의혹 제기. 추가 하락 가능성 및 매수 금지 의견.</t>
+          <t>제2임상시험 결과 발표 및 하한가 기록. 개인 투자자들의 불만과 상장폐지 우려 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['하한가', '주가 조작', '매도']</t>
+          <t>['임상시험', '하한가', '상장폐지']</t>
         </is>
       </c>
       <c r="X19" t="n">

--- a/data/trending_integrated_20260921_15.xlsx
+++ b/data/trending_integrated_20260921_15.xlsx
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>204398906785</v>
+        <v>204479858285</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10570</v>
+        <v>10520</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.18%</t>
+          <t>'+16.63%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.09</v>
       </c>
       <c r="E3" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F3" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G3" t="n">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="H3" t="n">
         <v>8.6</v>
@@ -702,7 +702,7 @@
         <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>272532022840</v>
+        <v>278318098520</v>
       </c>
       <c r="P3" t="n">
         <v>11640</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20650</v>
+        <v>21200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+11.80%</t>
+          <t>'+14.78%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="F4" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G4" t="n">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="H4" t="n">
         <v>1.25</v>
@@ -794,7 +794,7 @@
         <v>0.98</v>
       </c>
       <c r="O4" t="n">
-        <v>129778796995</v>
+        <v>133716979070</v>
       </c>
       <c r="P4" t="n">
         <v>21950</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32000</v>
+        <v>32100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.93%</t>
+          <t>'+8.26%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.48</v>
       </c>
       <c r="E5" t="n">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="F5" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="G5" t="n">
-        <v>2296</v>
+        <v>2336</v>
       </c>
       <c r="H5" t="n">
         <v>16.67</v>
@@ -886,7 +886,7 @@
         <v>17.15</v>
       </c>
       <c r="O5" t="n">
-        <v>44773437825</v>
+        <v>45218663575</v>
       </c>
       <c r="P5" t="n">
         <v>69200</v>
@@ -946,13 +946,13 @@
         <v>-0.31</v>
       </c>
       <c r="E6" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F6" t="n">
         <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="H6" t="n">
         <v>0.19</v>
@@ -978,7 +978,7 @@
         <v>0.5</v>
       </c>
       <c r="O6" t="n">
-        <v>63216838860</v>
+        <v>63569275065</v>
       </c>
       <c r="P6" t="n">
         <v>13140</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>208000</v>
+        <v>207500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.07%</t>
+          <t>'+5.81%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F7" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G7" t="n">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="H7" t="n">
         <v>75.44</v>
@@ -1070,7 +1070,7 @@
         <v>75.53</v>
       </c>
       <c r="O7" t="n">
-        <v>781078743050</v>
+        <v>798660057050</v>
       </c>
       <c r="P7" t="n">
         <v>243500</v>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11030</v>
+        <v>273500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.85%</t>
+          <t>'+4.79%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.16</v>
+        <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>151</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>86</v>
+        <v>507</v>
       </c>
       <c r="G8" t="n">
-        <v>477</v>
+        <v>2528</v>
       </c>
       <c r="H8" t="n">
-        <v>18.29</v>
+        <v>46.46</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>10520</v>
+        <v>261000</v>
       </c>
       <c r="K8" t="n">
-        <v>10780</v>
+        <v>264000</v>
       </c>
       <c r="L8" t="n">
-        <v>12190</v>
+        <v>275000</v>
       </c>
       <c r="M8" t="n">
-        <v>10590</v>
+        <v>263500</v>
       </c>
       <c r="N8" t="n">
-        <v>18.13</v>
+        <v>46.48</v>
       </c>
       <c r="O8" t="n">
-        <v>210552152555</v>
+        <v>5449579530750</v>
       </c>
       <c r="P8" t="n">
-        <v>22450</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>1760</v>
+        <v>81100</v>
       </c>
       <c r="R8" t="n">
-        <v>-70000</v>
+        <v>5703000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1431000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>11500원 돌파 시 고점 돌파 전망. 연기금 매수세 유입 및 공시 가능성 언급.</t>
+          <t>외인 및 기관의 쌍끌이 매수세 확인, 3분기 잠정실적 발표 및 4분기 자사주 소각/배당 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['연기금', '공시', '매물대']</t>
+          <t>['배당금', '잠정실적', '외인 매수']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>6</v>
+        <v>110</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>273500</v>
+        <v>11020</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.79%</t>
+          <t>'+4.75%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.02</v>
+        <v>0.16</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>152</v>
       </c>
       <c r="F9" t="n">
-        <v>509</v>
+        <v>86</v>
       </c>
       <c r="G9" t="n">
-        <v>2535</v>
+        <v>459</v>
       </c>
       <c r="H9" t="n">
-        <v>46.46</v>
+        <v>18.29</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>261000</v>
+        <v>10520</v>
       </c>
       <c r="K9" t="n">
-        <v>264000</v>
+        <v>10780</v>
       </c>
       <c r="L9" t="n">
-        <v>275000</v>
+        <v>12190</v>
       </c>
       <c r="M9" t="n">
-        <v>263500</v>
+        <v>10590</v>
       </c>
       <c r="N9" t="n">
-        <v>46.48</v>
+        <v>18.13</v>
       </c>
       <c r="O9" t="n">
-        <v>5347635663750</v>
+        <v>211767599495</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>22450</v>
       </c>
       <c r="Q9" t="n">
-        <v>81100</v>
+        <v>1760</v>
       </c>
       <c r="R9" t="n">
-        <v>5703000</v>
+        <v>-70000</v>
       </c>
       <c r="S9" t="n">
-        <v>1431000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>외인 매수세 유입에 따른 상승 기대감 존재. 배당금 및 잠정실적 발표 예정.</t>
+          <t>점심 이후 상승 기대감 있으나, 공시 내용 부재로 인한 불확실성 존재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['배당금', '실적발표', '외인매수']</t>
+          <t>['매물대', '종가', '공시']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1861000</v>
+        <v>1864000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.22%</t>
+          <t>'+0.38%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="G10" t="n">
-        <v>2306</v>
+        <v>2278</v>
       </c>
       <c r="H10" t="n">
         <v>50.23</v>
@@ -1346,7 +1346,7 @@
         <v>50.1</v>
       </c>
       <c r="O10" t="n">
-        <v>4346854184500</v>
+        <v>4434226765500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>반도체 수출 호조 기대감 속 주가 상승 전망. 신한증권 전산 오류로 인한 불편 호소.</t>
+          <t>반도체 수출 호조 기대감 속 190만 돌파 시 로켓 발사 전망, 신한증권 앱 오류 발생.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체수출', '신한증권', '주가상승']</t>
+          <t>['반도체 수출', '신한증권', '로켓']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26650</v>
+        <v>26750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.56%</t>
+          <t>'-0.19%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.3</v>
       </c>
       <c r="E11" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="H11" t="n">
         <v>2.11</v>
@@ -1438,7 +1438,7 @@
         <v>2.41</v>
       </c>
       <c r="O11" t="n">
-        <v>130399465500</v>
+        <v>133331679975</v>
       </c>
       <c r="P11" t="n">
         <v>59600</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>318000</v>
+        <v>316500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.75%</t>
+          <t>'-3.21%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>85</v>
       </c>
       <c r="G12" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H12" t="n">
         <v>3.62</v>
@@ -1530,7 +1530,7 @@
         <v>1.96</v>
       </c>
       <c r="O12" t="n">
-        <v>97393623250</v>
+        <v>98670863250</v>
       </c>
       <c r="P12" t="n">
         <v>635000</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18320</v>
+        <v>18300</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.12%</t>
+          <t>'-3.23%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G13" t="n">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="H13" t="n">
         <v>10.74</v>
@@ -1622,7 +1622,7 @@
         <v>10.74</v>
       </c>
       <c r="O13" t="n">
-        <v>85232207130</v>
+        <v>86904971260</v>
       </c>
       <c r="P13" t="n">
         <v>40350</v>
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13400</v>
+        <v>17720</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.39%</t>
+          <t>'-3.28%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.58</v>
+        <v>3.29</v>
       </c>
       <c r="E14" t="n">
-        <v>91</v>
+        <v>269</v>
       </c>
       <c r="F14" t="n">
-        <v>50</v>
+        <v>159</v>
       </c>
       <c r="G14" t="n">
-        <v>467</v>
+        <v>1219</v>
       </c>
       <c r="H14" t="n">
-        <v>5.5</v>
+        <v>7.9</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,91 +1699,91 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>13870</v>
+        <v>18320</v>
       </c>
       <c r="K14" t="n">
-        <v>14070</v>
+        <v>18450</v>
       </c>
       <c r="L14" t="n">
-        <v>14790</v>
+        <v>18590</v>
       </c>
       <c r="M14" t="n">
-        <v>13350</v>
+        <v>17560</v>
       </c>
       <c r="N14" t="n">
-        <v>4.92</v>
+        <v>4.61</v>
       </c>
       <c r="O14" t="n">
-        <v>76443292810</v>
+        <v>228634763025</v>
       </c>
       <c r="P14" t="n">
-        <v>30200</v>
+        <v>31500</v>
       </c>
       <c r="Q14" t="n">
-        <v>3540</v>
+        <v>1272</v>
       </c>
       <c r="R14" t="n">
-        <v>-382000</v>
+        <v>-1828000</v>
       </c>
       <c r="S14" t="n">
-        <v>-14000</v>
+        <v>-4000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
+          <t>기관 매수세와 함께 미국 광통신 AI 주식 급등 수혜 기대. 투자주의 종목 지정 및 CB 발행.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전', '신한투자증권', '공매도']</t>
+          <t>['기관 매수', '광통신 AI', '투자주의']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17665</v>
+        <v>13400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.58%</t>
+          <t>'-3.39%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.29</v>
+        <v>0.58</v>
       </c>
       <c r="E15" t="n">
-        <v>266</v>
+        <v>91</v>
       </c>
       <c r="F15" t="n">
-        <v>157</v>
+        <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>1202</v>
+        <v>480</v>
       </c>
       <c r="H15" t="n">
-        <v>7.9</v>
+        <v>5.5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,60 +1791,60 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>18320</v>
+        <v>13870</v>
       </c>
       <c r="K15" t="n">
-        <v>18450</v>
+        <v>14070</v>
       </c>
       <c r="L15" t="n">
-        <v>18590</v>
+        <v>14790</v>
       </c>
       <c r="M15" t="n">
-        <v>17560</v>
+        <v>13350</v>
       </c>
       <c r="N15" t="n">
-        <v>4.61</v>
+        <v>4.92</v>
       </c>
       <c r="O15" t="n">
-        <v>225068246005</v>
+        <v>77337434785</v>
       </c>
       <c r="P15" t="n">
-        <v>31500</v>
+        <v>30200</v>
       </c>
       <c r="Q15" t="n">
-        <v>1272</v>
+        <v>3540</v>
       </c>
       <c r="R15" t="n">
-        <v>-1828000</v>
+        <v>-382000</v>
       </c>
       <c r="S15" t="n">
-        <v>-4000</v>
+        <v>-14000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>기관 매수세와 함께 미국 광통신 AI 주식 급등 수혜 기대. 투자주의 종목 지정 및 CB 발행.</t>
+          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['기관 매수', '광통신 AI', '투자주의']</t>
+          <t>['원전', '신한투자증권', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
@@ -1866,13 +1866,13 @@
         <v>-0.22</v>
       </c>
       <c r="E16" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F16" t="n">
         <v>65</v>
       </c>
       <c r="G16" t="n">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="H16" t="n">
         <v>0.33</v>
@@ -1898,7 +1898,7 @@
         <v>0.55</v>
       </c>
       <c r="O16" t="n">
-        <v>32991284300</v>
+        <v>33614039005</v>
       </c>
       <c r="P16" t="n">
         <v>6480</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>76500</v>
+        <v>76400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.38%</t>
+          <t>'-4.50%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="F17" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G17" t="n">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="H17" t="n">
         <v>10.58</v>
@@ -1990,7 +1990,7 @@
         <v>10.68</v>
       </c>
       <c r="O17" t="n">
-        <v>120251588400</v>
+        <v>122753775650</v>
       </c>
       <c r="P17" t="n">
         <v>184000</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29850</v>
+        <v>29700</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.09%</t>
+          <t>'-5.56%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.48</v>
       </c>
       <c r="E18" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F18" t="n">
         <v>70</v>
       </c>
       <c r="G18" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H18" t="n">
         <v>11.92</v>
@@ -2076,13 +2076,13 @@
         <v>31550</v>
       </c>
       <c r="M18" t="n">
-        <v>29750</v>
+        <v>29700</v>
       </c>
       <c r="N18" t="n">
         <v>11.44</v>
       </c>
       <c r="O18" t="n">
-        <v>99435817975</v>
+        <v>103112714525</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>27100</v>
+        <v>27150</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-27.54%</t>
+          <t>'-27.41%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="G19" t="n">
-        <v>1620</v>
+        <v>1635</v>
       </c>
       <c r="H19" t="n">
         <v>7.09</v>
@@ -2174,7 +2174,7 @@
         <v>7.08</v>
       </c>
       <c r="O19" t="n">
-        <v>121281027200</v>
+        <v>121945012850</v>
       </c>
       <c r="P19" t="n">
         <v>146600</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>제2임상시험 결과 발표 및 하한가 기록. 개인 투자자들의 불만과 상장폐지 우려 제기.</t>
+          <t>제2임상시험 결과 발표 앞두고 하한가 반복, 개인 투자자 매도세 관측.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['임상시험', '하한가', '상장폐지']</t>
+          <t>['임상시험', '하한가', '매도세']</t>
         </is>
       </c>
       <c r="X19" t="n">

--- a/data/trending_integrated_20260921_15.xlsx
+++ b/data/trending_integrated_20260921_15.xlsx
@@ -584,7 +584,7 @@
         <v>134</v>
       </c>
       <c r="G2" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>204479858285</v>
+        <v>204485362785</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10520</v>
+        <v>10550</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.63%</t>
+          <t>'+16.96%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.09</v>
       </c>
       <c r="E3" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G3" t="n">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="H3" t="n">
         <v>8.6</v>
@@ -702,7 +702,7 @@
         <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>278318098520</v>
+        <v>280160708770</v>
       </c>
       <c r="P3" t="n">
         <v>11640</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>강한 거래대금을 동반한 주가 상승세, 후공정 대장주로서의 기대감. 향후 연간 수익성 개선 전망.</t>
+          <t>거래대금 동반 상승세와 함께 후공정 대장주로서 강한 상승 기대감이 형성되고 있으며, 향후 실적 전망도 긍정적으로 평가됨.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['거래대금', '후공정', '수익성']</t>
+          <t>['상승', '거래대금', '실적']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21200</v>
+        <v>21500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.78%</t>
+          <t>'+16.40%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F4" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G4" t="n">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="H4" t="n">
         <v>1.25</v>
@@ -794,7 +794,7 @@
         <v>0.98</v>
       </c>
       <c r="O4" t="n">
-        <v>133716979070</v>
+        <v>135460156070</v>
       </c>
       <c r="P4" t="n">
         <v>21950</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>국내 유일 혈관 치료 기술 확장 기대감. 글로벌 3상 동시 돌입 소식에 따른 주가 상승 전망.</t>
+          <t>혈관 치료 기술의 확장성과 신약 개발 성공 기대감이 주가 상승 요인으로 작용하고 있으며, 대규모 투자 유치 및 임상 3상 진입 소식이 긍정적으로 해석됨.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['혈관치료', '3상돌입', '기술확장']</t>
+          <t>['신약', '기술', '임상']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32100</v>
+        <v>5860</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.26%</t>
+          <t>'+7.92%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.48</v>
+        <v>-0.31</v>
       </c>
       <c r="E5" t="n">
-        <v>524</v>
+        <v>77</v>
       </c>
       <c r="F5" t="n">
-        <v>292</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>2336</v>
+        <v>215</v>
       </c>
       <c r="H5" t="n">
-        <v>16.67</v>
+        <v>0.19</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>29650</v>
+        <v>5430</v>
       </c>
       <c r="K5" t="n">
-        <v>30400</v>
+        <v>5710</v>
       </c>
       <c r="L5" t="n">
-        <v>33400</v>
+        <v>6280</v>
       </c>
       <c r="M5" t="n">
-        <v>29400</v>
+        <v>5600</v>
       </c>
       <c r="N5" t="n">
-        <v>17.15</v>
+        <v>0.5</v>
       </c>
       <c r="O5" t="n">
-        <v>45218663575</v>
+        <v>63852793585</v>
       </c>
       <c r="P5" t="n">
-        <v>69200</v>
+        <v>13140</v>
       </c>
       <c r="Q5" t="n">
-        <v>24150</v>
+        <v>3725</v>
       </c>
       <c r="R5" t="n">
-        <v>-133000</v>
+        <v>-347000</v>
       </c>
       <c r="S5" t="n">
-        <v>-4000</v>
+        <v>26000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>FDA 신약 승인 관련 기대와 회의론 혼재. 담관암 임상 결과 및 외인 매도 동향 주목.</t>
+          <t>비트코인 가격 상승 반전에 따라 우리기술투자 주가 급등. 신한투자증권 공매도 의혹 제기 및 민원 제기 움직임. 7천 원 목표가 제시하며 비트코인 흐름에 따른 주가 상승 기대감 형성.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['FDA 승인', '담관암', '리보세라닙']</t>
+          <t>['비트코인', '공매도', '신한투자증권']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,43 +919,43 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>041190</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5840</v>
+        <v>31950</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.55%</t>
+          <t>'+7.76%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.31</v>
+        <v>-0.48</v>
       </c>
       <c r="E6" t="n">
-        <v>76</v>
+        <v>530</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>295</v>
       </c>
       <c r="G6" t="n">
-        <v>210</v>
+        <v>2346</v>
       </c>
       <c r="H6" t="n">
-        <v>0.19</v>
+        <v>16.67</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>5430</v>
+        <v>29650</v>
       </c>
       <c r="K6" t="n">
-        <v>5710</v>
+        <v>30400</v>
       </c>
       <c r="L6" t="n">
-        <v>6280</v>
+        <v>33400</v>
       </c>
       <c r="M6" t="n">
-        <v>5600</v>
+        <v>29400</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5</v>
+        <v>17.15</v>
       </c>
       <c r="O6" t="n">
-        <v>63569275065</v>
+        <v>45705837175</v>
       </c>
       <c r="P6" t="n">
-        <v>13140</v>
+        <v>69200</v>
       </c>
       <c r="Q6" t="n">
-        <v>3725</v>
+        <v>24150</v>
       </c>
       <c r="R6" t="n">
-        <v>-347000</v>
+        <v>-133000</v>
       </c>
       <c r="S6" t="n">
-        <v>26000</v>
+        <v>-4000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>비트코인 가격 상승 반전에 따라 우리기술투자 주가 급등. 신한투자증권 공매도 의혹 제기 및 민원 제기 움직임. 7천 원 목표가 제시하며 비트코인 흐름에 따른 주가 상승 기대감 형성.</t>
+          <t>FDA 신약 승인 관련 기대와 회의론 혼재. 담관암 임상 결과 및 외인 매도 동향 주목.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['비트코인', '공매도', '신한투자증권']</t>
+          <t>['FDA 승인', '담관암', '리보세라닙']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>207500</v>
+        <v>208000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.81%</t>
+          <t>'+6.07%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F7" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G7" t="n">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="H7" t="n">
         <v>75.44</v>
@@ -1070,7 +1070,7 @@
         <v>75.53</v>
       </c>
       <c r="O7" t="n">
-        <v>798660057050</v>
+        <v>833255657050</v>
       </c>
       <c r="P7" t="n">
         <v>243500</v>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>273500</v>
+        <v>11060</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.79%</t>
+          <t>'+5.13%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.02</v>
+        <v>0.16</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>152</v>
       </c>
       <c r="F8" t="n">
-        <v>507</v>
+        <v>86</v>
       </c>
       <c r="G8" t="n">
-        <v>2528</v>
+        <v>461</v>
       </c>
       <c r="H8" t="n">
-        <v>46.46</v>
+        <v>18.29</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>261000</v>
+        <v>10520</v>
       </c>
       <c r="K8" t="n">
-        <v>264000</v>
+        <v>10780</v>
       </c>
       <c r="L8" t="n">
-        <v>275000</v>
+        <v>12190</v>
       </c>
       <c r="M8" t="n">
-        <v>263500</v>
+        <v>10590</v>
       </c>
       <c r="N8" t="n">
-        <v>46.48</v>
+        <v>18.13</v>
       </c>
       <c r="O8" t="n">
-        <v>5449579530750</v>
+        <v>212304684155</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>22450</v>
       </c>
       <c r="Q8" t="n">
-        <v>81100</v>
+        <v>1760</v>
       </c>
       <c r="R8" t="n">
-        <v>5703000</v>
+        <v>-70000</v>
       </c>
       <c r="S8" t="n">
-        <v>1431000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>외인 및 기관의 쌍끌이 매수세 확인, 3분기 잠정실적 발표 및 4분기 자사주 소각/배당 기대감.</t>
+          <t>점심 이후 상승 기대감 있으나, 공시 내용 부재로 인한 불확실성 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['배당금', '잠정실적', '외인 매수']</t>
+          <t>['매물대', '종가', '공시']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11020</v>
+        <v>274000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.75%</t>
+          <t>'+4.98%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.16</v>
+        <v>-0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>152</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>86</v>
+        <v>504</v>
       </c>
       <c r="G9" t="n">
-        <v>459</v>
+        <v>2601</v>
       </c>
       <c r="H9" t="n">
-        <v>18.29</v>
+        <v>46.46</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>10520</v>
+        <v>261000</v>
       </c>
       <c r="K9" t="n">
-        <v>10780</v>
+        <v>264000</v>
       </c>
       <c r="L9" t="n">
-        <v>12190</v>
+        <v>275000</v>
       </c>
       <c r="M9" t="n">
-        <v>10590</v>
+        <v>263500</v>
       </c>
       <c r="N9" t="n">
-        <v>18.13</v>
+        <v>46.48</v>
       </c>
       <c r="O9" t="n">
-        <v>211767599495</v>
+        <v>5853217150750</v>
       </c>
       <c r="P9" t="n">
-        <v>22450</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>1760</v>
+        <v>81100</v>
       </c>
       <c r="R9" t="n">
-        <v>-70000</v>
+        <v>5703000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1431000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>점심 이후 상승 기대감 있으나, 공시 내용 부재로 인한 불확실성 존재.</t>
+          <t>외국인 순매수세 유입과 공매도 물량 감소 추세 속에서 주가 상승 기대감이 형성되고 있으나, 정치적 이슈에 대한 언급도 존재함.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['매물대', '종가', '공시']</t>
+          <t>['외국인', '공매도', '배당']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>110</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1864000</v>
+        <v>1868000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.38%</t>
+          <t>'+0.59%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G10" t="n">
-        <v>2278</v>
+        <v>2272</v>
       </c>
       <c r="H10" t="n">
         <v>50.23</v>
@@ -1346,7 +1346,7 @@
         <v>50.1</v>
       </c>
       <c r="O10" t="n">
-        <v>4434226765500</v>
+        <v>4798608185500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>반도체 수출 호조 기대감 속 190만 돌파 시 로켓 발사 전망, 신한증권 앱 오류 발생.</t>
+          <t>반도체 수출 호조 및 해외 증시 상승 기대감으로 주가 상승 전망이 제시되나, 일부 증권사 앱 접속 오류가 언급됨.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체 수출', '신한증권', '로켓']</t>
+          <t>['반도체', '수출', '상승']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26750</v>
+        <v>26850</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.19%</t>
+          <t>'+0.19%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.3</v>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G11" t="n">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="H11" t="n">
         <v>2.11</v>
@@ -1438,7 +1438,7 @@
         <v>2.41</v>
       </c>
       <c r="O11" t="n">
-        <v>133331679975</v>
+        <v>134295111675</v>
       </c>
       <c r="P11" t="n">
         <v>59600</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>316500</v>
+        <v>318500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.21%</t>
+          <t>'-2.60%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>1.66</v>
       </c>
       <c r="E12" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F12" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G12" t="n">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="H12" t="n">
         <v>3.62</v>
@@ -1530,7 +1530,7 @@
         <v>1.96</v>
       </c>
       <c r="O12" t="n">
-        <v>98670863250</v>
+        <v>100438538250</v>
       </c>
       <c r="P12" t="n">
         <v>635000</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>52주 신고가 돌파 및 기관 목표가 상향 기대감. 외국인 재유입 신호 감지.</t>
+          <t>52주 신고가 돌파 및 기관 목표가 상향 조정에 따라 주가 상승에 대한 기대감이 높으며, 외국인 매수세 유입도 긍정적인 신호로 작용하고 있음.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['52주 신고가', '기관 목표가', '외국인 유입']</t>
+          <t>['신고가', '기관', '외국인']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18300</v>
+        <v>18290</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.23%</t>
+          <t>'-3.28%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F13" t="n">
         <v>67</v>
       </c>
       <c r="G13" t="n">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="H13" t="n">
         <v>10.74</v>
@@ -1622,7 +1622,7 @@
         <v>10.74</v>
       </c>
       <c r="O13" t="n">
-        <v>86904971260</v>
+        <v>87680558710</v>
       </c>
       <c r="P13" t="n">
         <v>40350</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>공매도 세력에 대한 불만과 주가 상승 의지 표출. 추세 전환 기대감 있으나 근거 부족.</t>
+          <t>공매도 및 대차 관련 부정적 언급과 함께 주가 상승에 대한 기대감도 있으나, 정부 정책 및 투자자 단결에 대한 요구가 강함.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '대차해지', '주가정상화']</t>
+          <t>['공매도', '대차', '유상증자']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1682,13 +1682,13 @@
         <v>3.29</v>
       </c>
       <c r="E14" t="n">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="F14" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G14" t="n">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="H14" t="n">
         <v>7.9</v>
@@ -1714,7 +1714,7 @@
         <v>4.61</v>
       </c>
       <c r="O14" t="n">
-        <v>228634763025</v>
+        <v>230197578425</v>
       </c>
       <c r="P14" t="n">
         <v>31500</v>
@@ -1774,10 +1774,10 @@
         <v>0.58</v>
       </c>
       <c r="E15" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G15" t="n">
         <v>480</v>
@@ -1806,7 +1806,7 @@
         <v>4.92</v>
       </c>
       <c r="O15" t="n">
-        <v>77337434785</v>
+        <v>77836665185</v>
       </c>
       <c r="P15" t="n">
         <v>30200</v>
@@ -1866,13 +1866,13 @@
         <v>-0.22</v>
       </c>
       <c r="E16" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F16" t="n">
         <v>65</v>
       </c>
       <c r="G16" t="n">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="H16" t="n">
         <v>0.33</v>
@@ -1898,7 +1898,7 @@
         <v>0.55</v>
       </c>
       <c r="O16" t="n">
-        <v>33614039005</v>
+        <v>33951179815</v>
       </c>
       <c r="P16" t="n">
         <v>6480</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>76400</v>
+        <v>76500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.50%</t>
+          <t>'-4.38%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="F17" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G17" t="n">
-        <v>800</v>
+        <v>820</v>
       </c>
       <c r="H17" t="n">
         <v>10.58</v>
@@ -1990,7 +1990,7 @@
         <v>10.68</v>
       </c>
       <c r="O17" t="n">
-        <v>122753775650</v>
+        <v>125645628650</v>
       </c>
       <c r="P17" t="n">
         <v>184000</v>
@@ -2050,13 +2050,13 @@
         <v>0.48</v>
       </c>
       <c r="E18" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F18" t="n">
         <v>70</v>
       </c>
       <c r="G18" t="n">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="H18" t="n">
         <v>11.92</v>
@@ -2082,7 +2082,7 @@
         <v>11.44</v>
       </c>
       <c r="O18" t="n">
-        <v>103112714525</v>
+        <v>106005999425</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>외인 및 프로그램 매도세 지속, 28000원 복귀 및 급락 가능성. 투자 심리 위축.</t>
+          <t>주가 하락 및 매도 물량 증가에 대한 언급이 다수이며, 개인 투자자들의 불안감이 나타나고 있음. 일부는 보유 물량을 정리함.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['매도', '급락', '반도체']</t>
+          <t>['매도', '하락', '외국인']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>27150</v>
+        <v>27300</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-27.41%</t>
+          <t>'-27.01%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G19" t="n">
-        <v>1635</v>
+        <v>1627</v>
       </c>
       <c r="H19" t="n">
         <v>7.09</v>
@@ -2174,7 +2174,7 @@
         <v>7.08</v>
       </c>
       <c r="O19" t="n">
-        <v>121945012850</v>
+        <v>122677471850</v>
       </c>
       <c r="P19" t="n">
         <v>146600</v>

--- a/data/trending_integrated_20260921_15.xlsx
+++ b/data/trending_integrated_20260921_15.xlsx
@@ -584,7 +584,7 @@
         <v>134</v>
       </c>
       <c r="G2" t="n">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>204485362785</v>
+        <v>204486574785</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>美 타임지 선정 '세계 최고 헬스테크 기업' 선정 소식에 따른 주가 급등. 향후 추가 상승 기대.</t>
+          <t>美 타임지 선정 최고 헬스테크 기업 선정 등 호재 기반 급등세. 단기 변동성 유의.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['헬스테크', '타임지선정', '급등']</t>
+          <t>['헬스테크', '기업 선정', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>0.09</v>
       </c>
       <c r="E3" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F3" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G3" t="n">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="H3" t="n">
         <v>8.6</v>
@@ -702,7 +702,7 @@
         <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>280160708770</v>
+        <v>280262220870</v>
       </c>
       <c r="P3" t="n">
         <v>11640</v>
@@ -762,13 +762,13 @@
         <v>0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F4" t="n">
         <v>79</v>
       </c>
       <c r="G4" t="n">
-        <v>375</v>
+        <v>424</v>
       </c>
       <c r="H4" t="n">
         <v>1.25</v>
@@ -794,7 +794,7 @@
         <v>0.98</v>
       </c>
       <c r="O4" t="n">
-        <v>135460156070</v>
+        <v>135503371070</v>
       </c>
       <c r="P4" t="n">
         <v>21950</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>혈관 치료 기술의 확장성과 신약 개발 성공 기대감이 주가 상승 요인으로 작용하고 있으며, 대규모 투자 유치 및 임상 3상 진입 소식이 긍정적으로 해석됨.</t>
+          <t>국내 유일 혈관 치료 기술 기반 신약 개발 기대감 및 글로벌 임상 3상 진입. 기관 순매수.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['신약', '기술', '임상']</t>
+          <t>['혈관 치료', '신약 개발', '임상 3상']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -854,13 +854,13 @@
         <v>-0.31</v>
       </c>
       <c r="E5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G5" t="n">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H5" t="n">
         <v>0.19</v>
@@ -886,7 +886,7 @@
         <v>0.5</v>
       </c>
       <c r="O5" t="n">
-        <v>63852793585</v>
+        <v>63864947225</v>
       </c>
       <c r="P5" t="n">
         <v>13140</v>
@@ -946,13 +946,13 @@
         <v>-0.48</v>
       </c>
       <c r="E6" t="n">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="F6" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="G6" t="n">
-        <v>2346</v>
+        <v>2370</v>
       </c>
       <c r="H6" t="n">
         <v>16.67</v>
@@ -1038,13 +1038,13 @@
         <v>-0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F7" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G7" t="n">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="H7" t="n">
         <v>75.44</v>
@@ -1070,7 +1070,7 @@
         <v>75.53</v>
       </c>
       <c r="O7" t="n">
-        <v>833255657050</v>
+        <v>833743833050</v>
       </c>
       <c r="P7" t="n">
         <v>243500</v>
@@ -1130,13 +1130,13 @@
         <v>0.16</v>
       </c>
       <c r="E8" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F8" t="n">
         <v>86</v>
       </c>
       <c r="G8" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H8" t="n">
         <v>18.29</v>
@@ -1162,7 +1162,7 @@
         <v>18.13</v>
       </c>
       <c r="O8" t="n">
-        <v>212304684155</v>
+        <v>212337200555</v>
       </c>
       <c r="P8" t="n">
         <v>22450</v>
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="G9" t="n">
-        <v>2601</v>
+        <v>2659</v>
       </c>
       <c r="H9" t="n">
         <v>46.46</v>
@@ -1254,7 +1254,7 @@
         <v>46.48</v>
       </c>
       <c r="O9" t="n">
-        <v>5853217150750</v>
+        <v>5853546498750</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>외국인 순매수세 유입과 공매도 물량 감소 추세 속에서 주가 상승 기대감이 형성되고 있으나, 정치적 이슈에 대한 언급도 존재함.</t>
+          <t>외인 프로그램 매수세 유입 및 배당 기대감 속 단기 하락 제한 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외국인', '공매도', '배당']</t>
+          <t>['공매도', '배당', '외인 매수']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="G10" t="n">
-        <v>2272</v>
+        <v>2237</v>
       </c>
       <c r="H10" t="n">
         <v>50.23</v>
@@ -1346,7 +1346,7 @@
         <v>50.1</v>
       </c>
       <c r="O10" t="n">
-        <v>4798608185500</v>
+        <v>4798845421500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>반도체 수출 호조 및 해외 증시 상승 기대감으로 주가 상승 전망이 제시되나, 일부 증권사 앱 접속 오류가 언급됨.</t>
+          <t>반도체 수출 호조 기대감 속 개인 매도세 전환 및 상승 추세 유지 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체', '수출', '상승']</t>
+          <t>['반도체 수출', '개인 매도', '상승 추세']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1406,13 +1406,13 @@
         <v>-0.3</v>
       </c>
       <c r="E11" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F11" t="n">
         <v>43</v>
       </c>
       <c r="G11" t="n">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="H11" t="n">
         <v>2.11</v>
@@ -1438,7 +1438,7 @@
         <v>2.41</v>
       </c>
       <c r="O11" t="n">
-        <v>134295111675</v>
+        <v>134355953775</v>
       </c>
       <c r="P11" t="n">
         <v>59600</v>
@@ -1504,7 +1504,7 @@
         <v>87</v>
       </c>
       <c r="G12" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H12" t="n">
         <v>3.62</v>
@@ -1530,7 +1530,7 @@
         <v>1.96</v>
       </c>
       <c r="O12" t="n">
-        <v>100438538250</v>
+        <v>100445226750</v>
       </c>
       <c r="P12" t="n">
         <v>635000</v>
@@ -1590,13 +1590,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F13" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G13" t="n">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="H13" t="n">
         <v>10.74</v>
@@ -1622,7 +1622,7 @@
         <v>10.74</v>
       </c>
       <c r="O13" t="n">
-        <v>87680558710</v>
+        <v>87716699750</v>
       </c>
       <c r="P13" t="n">
         <v>40350</v>
@@ -1682,13 +1682,13 @@
         <v>3.29</v>
       </c>
       <c r="E14" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F14" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G14" t="n">
-        <v>1227</v>
+        <v>1236</v>
       </c>
       <c r="H14" t="n">
         <v>7.9</v>
@@ -1714,7 +1714,7 @@
         <v>4.61</v>
       </c>
       <c r="O14" t="n">
-        <v>230197578425</v>
+        <v>230333862945</v>
       </c>
       <c r="P14" t="n">
         <v>31500</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>기관 매수세와 함께 미국 광통신 AI 주식 급등 수혜 기대. 투자주의 종목 지정 및 CB 발행.</t>
+          <t>미국 광통신주 급등과 연계된 상승 기대감 있으나, 투자주의 종목 지정 및 기관 매도 압력.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['기관 매수', '광통신 AI', '투자주의']</t>
+          <t>['광통신', '투자주의', '기관 매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1806,7 +1806,7 @@
         <v>4.92</v>
       </c>
       <c r="O15" t="n">
-        <v>77836665185</v>
+        <v>77849314785</v>
       </c>
       <c r="P15" t="n">
         <v>30200</v>
@@ -1866,13 +1866,13 @@
         <v>-0.22</v>
       </c>
       <c r="E16" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G16" t="n">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="H16" t="n">
         <v>0.33</v>
@@ -1898,7 +1898,7 @@
         <v>0.55</v>
       </c>
       <c r="O16" t="n">
-        <v>33951179815</v>
+        <v>33975019160</v>
       </c>
       <c r="P16" t="n">
         <v>6480</v>
@@ -1958,13 +1958,13 @@
         <v>-0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F17" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G17" t="n">
-        <v>820</v>
+        <v>840</v>
       </c>
       <c r="H17" t="n">
         <v>10.58</v>
@@ -2050,13 +2050,13 @@
         <v>0.48</v>
       </c>
       <c r="E18" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F18" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G18" t="n">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="H18" t="n">
         <v>11.92</v>
@@ -2082,7 +2082,7 @@
         <v>11.44</v>
       </c>
       <c r="O18" t="n">
-        <v>106005999425</v>
+        <v>106160231525</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>주가 하락 및 매도 물량 증가에 대한 언급이 다수이며, 개인 투자자들의 불안감이 나타나고 있음. 일부는 보유 물량을 정리함.</t>
+          <t>잦은 급등락 및 투자 심리 위축, 추가 하락 가능성에 대한 우려.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['매도', '하락', '외국인']</t>
+          <t>['급등락', '투자 심리', '하락']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="G19" t="n">
-        <v>1627</v>
+        <v>1616</v>
       </c>
       <c r="H19" t="n">
         <v>7.09</v>
@@ -2174,7 +2174,7 @@
         <v>7.08</v>
       </c>
       <c r="O19" t="n">
-        <v>122677471850</v>
+        <v>122677526450</v>
       </c>
       <c r="P19" t="n">
         <v>146600</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>제2임상시험 결과 발표 앞두고 하한가 반복, 개인 투자자 매도세 관측.</t>
+          <t>하한가 기록 및 급락세 지속, 투자자 주의 및 추가 하락 가능성 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['임상시험', '하한가', '매도세']</t>
+          <t>['하한가', '급락', '투자자 주의']</t>
         </is>
       </c>
       <c r="X19" t="n">
